--- a/spase_helio_compare/excel/long_Alternate_diff.xlsx
+++ b/spase_helio_compare/excel/long_Alternate_diff.xlsx
@@ -431,7357 +431,7357 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Solar Orbiter</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Solar Orbiter</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>AeroCube-6 CubeSat</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AeroCube-6 CubeSat</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>AeroCube-6A CubeSat</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AeroCube-6A CubeSat</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>AeroCube-6B CubeSat</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AeroCube-6B CubeSat</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Polarimeter to Unify the Corona and Heliosphere</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Polarimeter to Unify the Corona and Heliosphere</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Polarimeter to Unify the Corona and Heliosphere Narrow Field Imager</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Polarimeter to Unify the Corona and Heliosphere Narrow Field Imager</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Polarimeter to Unify the Corona and Heliosphere Wide Field Imager</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Polarimeter to Unify the Corona and Heliosphere Wide Field Imager</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Polarimeter to Unify the Corona and Heliosphere Wide-Field Imager 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Polarimeter to Unify the Corona and Heliosphere Wide-Field Imager 1</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Polarimeter to Unify the Corona and Heliosphere Wide-Field Imager 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Polarimeter to Unify the Corona and Heliosphere Wide-Field Imager 2</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Polarimeter to Unify the Corona and Heliosphere Wide-Field Imager 3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Polarimeter to Unify the Corona and Heliosphere Wide-Field Imager 3</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>['']</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
           <t>GO-ABOVE the Geospace Observatory - Array for
    Broadband Observations of VLF/ELF Emissions</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>['']</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Aeolus</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Aeolus</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Aeros-A</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>['1972-100A', 'Aeros 1']</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Aeros-A</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>AIM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AIM</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Advanced Modular Incoherent Scatter Radar (AMISR)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Advanced Modular Incoherent Scatter Radar (AMISR)</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Active Magnetospheric Particle Tracer Explorers</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Active Magnetospheric Particle Tracer Explorers</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Exploration of energization and Radiation in Geospace (ERG), now known as Arase</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Exploration of energization and Radiation in Geospace (ERG), now known as Arase</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Acceleration, Reconnection, Turbulence, Electrodynamics of the Moon’s Interaction with the Sun</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Acceleration, Reconnection, Turbulence, Electrodynamics of the Moon’s Interaction with the Sun</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BAS A80</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BAS A80</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BAS A81</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BAS A81</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BAS A84</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BAS A84</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Halley Bay</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Halley Bay</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>South Pole</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>South Pole</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Balloon Array for Radiation-belt Relativistic Electron Losses</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Balloon Array for Radiation-belt Relativistic Electron Losses</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 1A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BARREL Balloon 1A</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 1B</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BARREL Balloon 1B</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 1C</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BARREL Balloon 1C</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 1D</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BARREL Balloon 1D</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 1G</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BARREL Balloon 1G</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 1H</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BARREL Balloon 1H</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 1I</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BARREL Balloon 1I</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 1J</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BARREL Balloon 1J</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 1K</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BARREL Balloon 1K</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 1M</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BARREL Balloon 1M</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 1N</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BARREL Balloon 1N</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 1O</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BARREL Balloon 1O</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 1Q</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BARREL Balloon 1Q</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 1R</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BARREL Balloon 1R</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 1S</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BARREL Balloon 1S</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 1T</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BARREL Balloon 1T</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 1U</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BARREL Balloon 1U</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 1V</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BARREL Balloon 1V</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 2A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BARREL Balloon 2A</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 2B</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BARREL Balloon 2B</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 2C</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BARREL Balloon 2C</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 2D</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BARREL Balloon 2D</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 2E</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BARREL Balloon 2E</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 2F</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BARREL Balloon 2F</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 2I</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BARREL Balloon 2I</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 2K</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BARREL Balloon 2K</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 2L</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BARREL Balloon 2L</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 2M</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BARREL Balloon 2M</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 2N</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BARREL Balloon 2N</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 2O</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BARREL Balloon 2O</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 2P</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BARREL Balloon 2P</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 2Q</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BARREL Balloon 2Q</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 2T</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BARREL Balloon 2T</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 2W</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BARREL Balloon 2W</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 2X</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BARREL Balloon 2X</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 2Y</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BARREL Balloon 2Y</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 3A</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BARREL Balloon 3A</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 3B</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BARREL Balloon 3B</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 3C</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BARREL Balloon 3C</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 3D</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BARREL Balloon 3D</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 3E</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BARREL Balloon 3E</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 3F</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BARREL Balloon 3F</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 3G</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BARREL Balloon 3G</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 4A</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BARREL Balloon 4A</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 4B</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BARREL Balloon 4B</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 4C</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BARREL Balloon 4C</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 4D</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BARREL Balloon 4D</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 4E</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BARREL Balloon 4E</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 4F</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BARREL Balloon 4F</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 4G</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BARREL Balloon 4G</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 4H</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BARREL Balloon 4H</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 5A</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BARREL Balloon 5A</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 6A</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BARREL Balloon 6A</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BARREL Balloon 7A</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BARREL Balloon 7A</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Big Bear Solar Observatory (BBSO)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Big Bear Solar Observatory (BBSO)</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>BepiColombo Spacecraft</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BepiColombo Spacecraft</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>CHAMP</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CHAMP</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>CLIMAX</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CLIMAX</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>Communication/Navigation Outage Forecasting System</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>['Coupled Ion Neutral Dynamics Investigation (CINDI)']</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Communication/Navigation Outage Forecasting System</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>CONT</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CONT</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>CORONAS F</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>['KORONAS-F', 'AUS-SM-KF']</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>CORONAS F</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Dawn</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Dawn</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>DAWS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DAWS</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>Dynamics Explorer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t>['DE']</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Dynamics Explorer</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Daniel K Inouye Solar Telescope (DKIST)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Daniel K Inouye Solar Telescope (DKIST)</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>DMSP_5D-2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>DMSP_5D-2</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>Deep Space Climate Observatory</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>['2015-007A']</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Deep Space Climate Observatory</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Dunn Solar Telescope (DST)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dunn Solar Telescope (DST)</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Technical University of Denmark Magnetic Ground Stations</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Technical University of Denmark Magnetic Ground Stations</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>e-CALLISTO International Network of Solar Radio Spectrometers</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>e-CALLISTO International Network of Solar Radio Spectrometers</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Electron Losses and Fields Investigation A, CubeSat</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Electron Losses and Fields Investigation A, CubeSat</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Electron Losses and Fields Investigation B, CubeSat</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Electron Losses and Fields Investigation B, CubeSat</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Emirates Mars Mission (EMM)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Emirates Mars Mission (EMM)</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>ESKI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ESKI</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Explorer Spacecraft Series</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Explorer Spacecraft Series</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>Fast Auroral Snapshot</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>['1996-049A', 'Small Explorer/FAST', 'Explorer 70', 'SMEX/FAST', 'Fast Auroral SnapshoT Explorer']</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Fast Auroral Snapshot</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Fermi Gamma-ray Space Telescope</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Fermi Gamma-ray Space Telescope</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>MCMU</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MCMU</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>FSIM</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FSIM</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>FSMI</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FSMI</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>GILL</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GILL</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Giotto</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Giotto</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Gravity Field and Steady-State Ocean Circulation Explorer (GOCE)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Gravity Field and Steady-State Ocean Circulation Explorer (GOCE)</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>Geostationary Operational Environmental Satellites</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
           <t>['GOES Satellite Series']</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Geostationary Operational Environmental Satellites</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>Global-scale Observations of the Limb and Disk</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
           <t>['SES-14', '43175']</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Global-scale Observations of the Limb and Disk</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Gravity Recovery and Climate Experiment (GRACE)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Gravity Recovery and Climate Experiment (GRACE)</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Akulivik Geophysical Observatory</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Akulivik Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Amderma Geophysical Observatory</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Amderma Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Anchorage Geophysical Observatory</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Anchorage Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Andenes Geophysical Observatory</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Andenes Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Athabasca Geophysical Observatory</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Athabasca Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Attu Geophysical Observatory</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Attu Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Baker Lake Geophysical Observatory</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Baker Lake Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Baranov Geophysical Observatory</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Baranov Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Barentsburg Geophysical Observatory</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Barentsburg Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Barrow Geophysical Observatory</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Barrow Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Bennington Geophysical Observatory</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Bennington Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Bettles Geophysical Observatory</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Bettles Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Bjornoya Geophysical Observatory</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Bjornoya Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Boulder Geophysical Observatory</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Boulder Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Brorfelde Geophysical Observatory</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Brorfelde Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Cambridge Bay Geophysical Observatory</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Cambridge Bay Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Cape Dorset Geophysical Observatory</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cape Dorset Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Carson City Geophysical Observatory</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Carson City Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Chibougamau Geophysical Observatory</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Chibougamau Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Clyde River Geophysical Observatory</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Clyde River Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>College Geophysical Observatory</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>College Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Colville National Forest Geophysical Observatory</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Colville National Forest Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>CTIO</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>CTIO</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Daneborg Geophysical Observatory</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Daneborg Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Danmarkshavn Geophysical Observatory</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Danmarkshavn Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Dead Horse Geophysical Observatory</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Dead Horse Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Dededo Geophysical Observatory</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Dededo Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Derby Geophysical Observatory</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Derby Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Dikson Geophysical Observatory</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Dikson Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Dombas Geophysical Observatory</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Dombas Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Donna Geophysical Observatory</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Donna Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Eagle Geophysical Observatory</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Eagle Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>THEMIS-Associated Ground Magnetometer Stations</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>THEMIS-Associated Ground Magnetometer Stations</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Hankasalmi Geophysical Observatory</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Hankasalmi Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Hov Faroe Islands Geophysical Observatory</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Hov Faroe Islands Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Karmoy Geophysical Observatory</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Karmoy Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Learmonth</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Learmonth</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Leirvogur Geophysical Observatory</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Leirvogur Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Mid-continent Magnetoseismic Chain, McMAC, Observatory Chain</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Mid-continent Magnetoseismic Chain, McMAC, Observatory Chain</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Near Conjugate Northern Auroral Electrojet Index</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Near Conjugate Northern Auroral Electrojet Index</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Radisson Geophysical Observatory</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Radisson Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Romo Geophysical Observatory</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Romo Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Southern Auroral Electrojet Index</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Southern Auroral Electrojet Index</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Escudero</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Escudero</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Los Cerrillos</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Los Cerrillos</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Puerto Natales</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Puerto Natales</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Punta Arenas</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Punta Arenas</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Putre</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Putre</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Valdivia</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
+          <t>Solar Terrestrial Energy Program</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
           <t>['Solar-Terrestrial Energy Program, STEP, Polar Network', 'UAPM', 'Upper Atmospheric Monitoring Program']</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Solar Terrestrial Energy Program</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Tasiilaq Geophysical Observatory</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Tasiilaq Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>TEIDE Observatory</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>TEIDE Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Toolik Lake Geophysical Observatory</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Toolik Lake Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Trapper Creek Geophysical Observatory</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Trapper Creek Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
+          <t>Tromso Geophysical Observatory</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
           <t>['Observatory Station Code: TRO']</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Tromso Geophysical Observatory</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Udaipur</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Udaipur</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Upernavik Geophysical Observatory</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Upernavik Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>HANET Observatory Network</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>HANET Observatory Network</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Helios Mission</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Helios Mission</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>HEO-1</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>HEO-1</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>HEO-2</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>HEO-2</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>HEO-3</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>HEO-3</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Heliophysics Environmental and Radiation Measurement Experiment Suite (HERMES)</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Heliophysics Environmental and Radiation Measurement Experiment Suite (HERMES)</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Hinode</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Hinode</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Interstellar Boundary Explorer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Interstellar Boundary Explorer</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>AGO P1</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>AGO P1</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>AGO P2</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>AGO P2</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>AGO P3</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>AGO P3</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>AGO P4</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>AGO P4</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>AGO P5</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>AGO P5</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>AGO P6</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>AGO P6</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Gakona</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Gakona</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Iqaluit</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Iqaluit</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>McMurdo</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>McMurdo</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>South Pole</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>South Pole</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
+          <t>Ionospheric Connection</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
           <t>['ICON', '44628']</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Ionospheric Connection</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>IGPP-LANL Air Force Academy Magnetometer</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>IGPP-LANL Air Force Academy Magnetometer</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>IGPP-LANL Boulder Magnetometer</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>IGPP-LANL Boulder Magnetometer</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>IGPP-LANL Cambridge Magnetometer</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>IGPP-LANL Cambridge Magnetometer</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>IGPP-LANL Crete Magnetometer</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>IGPP-LANL Crete Magnetometer</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>IGPP-LANL Jicamarca Magnetometer</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>IGPP-LANL Jicamarca Magnetometer</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>IGPP-LANL Los Alamos National Laboratory Magnetometer</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>IGPP-LANL Los Alamos National Laboratory Magnetometer</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>IGPP-LANL Rapid City Magnetometer</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>IGPP-LANL Rapid City Magnetometer</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>IGPP-LANL San Gabriel Dam Magnetometer</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>IGPP-LANL San Gabriel Dam Magnetometer</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>IGPP-LANL SE Louisiana University Magnetometer</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>IGPP-LANL SE Louisiana University Magnetometer</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>IGPP-LANL Table Mountain Magnetometer</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>IGPP-LANL Table Mountain Magnetometer</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>IGPP-LANL Teoloyucan Magnetometer</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>IGPP-LANL Teoloyucan Magnetometer</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
+          <t>International GNSS Service</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
           <t>['International GPS Service']</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>International GNSS Service</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>IMP Spacecraft Series</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>IMP Spacecraft Series</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Interball Auroral</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Interball Auroral</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Interball Tail</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Interball Tail</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>IRIDIUM</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>IRIDIUM</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>IRIDIUM_1_70</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>IRIDIUM_1_70</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
+          <t>Interface Region Imaging Spectrograph</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
           <t>['2013-033A']</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Interface Region Imaging Spectrograph</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>International Sun-Earth Explorer</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>International Sun-Earth Explorer</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>ISLL</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>ISLL</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>International Space Station</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>International Space Station</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>JSPO</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>JSPO</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Kaguya (SELENE)</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Kaguya (SELENE)</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Korean Multi-Purpose Satellite (KOMPSAT-1)</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Korean Multi-Purpose Satellite (KOMPSAT-1)</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>KSO</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>KSO</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>LANL Spacecraft Series</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>LANL Spacecraft Series</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>LANL01A</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>LANL01A</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>LANL02A</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>LANL02A</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>LOFAR</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>LOFAR</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Mariner 10</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Mariner 10</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Mars Express</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Mars Express</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
+          <t>Mars Science Laboratory</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
           <t>['Curiosity']</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Mars Science Laboratory</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
+          <t>Mars Atmosphere and Volatile EvolutioN</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
           <t>['MAVEN']</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Mars Atmosphere and Volatile EvolutioN</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Mid-continent Magnetoseismic Chain (McMAC) Americus Station</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Mid-continent Magnetoseismic Chain (McMAC) Americus Station</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Mid-continent Magnetoseismic Chain (McMAC) Bennington Station</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Mid-continent Magnetoseismic Chain (McMAC) Bennington Station</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Mid-continent Magnetoseismic Chain (McMAC) Glyndon Station</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Mid-continent Magnetoseismic Chain (McMAC) Glyndon Station</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Mid-continent Magnetoseismic Chain (McMAC) Linares Station</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Mid-continent Magnetoseismic Chain (McMAC) Linares Station</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Mid-continent Magnetoseismic Chain (McMAC) Lyford Station</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Mid-continent Magnetoseismic Chain (McMAC) Lyford Station</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Mid-continent Magnetoseismic Chain (McMAC) Purcell Station</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Mid-continent Magnetoseismic Chain (McMAC) Purcell Station</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Mid-continent Magnetoseismic Chain (McMAC) Richardson Station</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Mid-continent Magnetoseismic Chain (McMAC) Richardson Station</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Mid-continent Magnetoseismic Chain (McMAC) San Antonio Station</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Mid-continent Magnetoseismic Chain (McMAC) San Antonio Station</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Mid-continent Magnetoseismic Chain (McMAC) Worthington Station</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Mid-continent Magnetoseismic Chain (McMAC) Worthington Station</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Applied Physics Lab Geomagnetic Observatory</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Applied Physics Lab Geomagnetic Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Bullcreek Observatory Geomagnetic Observatory</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Bullcreek Observatory Geomagnetic Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Clarkson University Geomagnetic Observatory</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Clarkson University Geomagnetic Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Darksky Observatory Geomagnetic Observatory</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Darksky Observatory Geomagnetic Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Grafton Test Facility Geomagnetic Observatory</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Grafton Test Facility Geomagnetic Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>The Jacksonville University Geomagnetic Observatory.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>The Jacksonville University Geomagnetic Observatory.</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>The Millstone Hill Geomagnetic Observatory.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>The Millstone Hill Geomagnetic Observatory.</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>The University of South Carolina Geomagnetic Observatory.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>The University of South Carolina Geomagnetic Observatory.</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>MetOp-A</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>MetOp-A</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>MetOp-A</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>MetOp-A</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Observatoire de Paris (Meudon site)</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Observatoire de Paris (Meudon site)</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
+          <t>Mars Global Surveyor</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
           <t>['1996-062A', 'MGS', '1996-062A']</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Mars Global Surveyor</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Magnetosphere-Ionosphere Coupling in the Alfvén resonator (MICA)</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Magnetosphere-Ionosphere Coupling in the Alfvén resonator (MICA)</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Magnetospheric Multiscale</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Magnetospheric Multiscale</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>MMS-1</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>MMS-1</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>MMS-2</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>MMS-2</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>MMS-3</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>MMS-3</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>MMS-4</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>MMS-4</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Munin Spacecraft</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Munin Spacecraft</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Neutron Monitor Stations</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Neutron Monitor Stations</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Fort Smith</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Fort Smith</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Inuvik</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Inuvik</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>McMurdo</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>McMurdo</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Nain</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Nain</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Peawanuck</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Peawanuck</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>South Pole</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>South Pole</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>SwarthmoreNewark</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>SwarthmoreNewark</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Thule</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Thule</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Climax</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Climax</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Haleakala</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Haleakala</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Huancayo</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Huancayo</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Nimbus 7</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Nimbus 7</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>NOAA 11</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>NOAA 11</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>NOAA 9</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>NOAA 9</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>NOB_RH</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>NOB_RH</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>NSO Observatory Group</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>NSO Observatory Group</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>OAC</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>OAC</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>ObsParis</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>ObsParis</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>OGO Satellites</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>OGO Satellites</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>OMNI</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>OMNI</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
+          <t>Parker Solar Probe</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
           <t>['PSP', 'Solar Probe Plus Spacecraft', 'SPP']</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Parker Solar Probe</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>PICARD</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PICARD</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Pic du Midi</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Pic du Midi</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>PINA</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PINA</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Pioneer Spacecraft Series</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Pioneer Spacecraft Series</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Polar-orbiting Operational Environmental Satellite (POES)</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Polar-orbiting Operational Environmental Satellite (POES)</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>PROBA2</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PROBA2</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Prognoz Spacecraft Series</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Prognoz Spacecraft Series</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>RABB</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>RABB</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Radio JOVE Observatory Network</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Radio JOVE Observatory Network</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>RANK</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>RANK</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Redline Emission Geospace Observatory (rEGO)</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Redline Emission Geospace Observatory (rEGO)</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Rocket Experiment for Neutral Upwelling 2</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Rocket Experiment for Neutral Upwelling 2</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
+          <t>Reuven Ramaty High Energy Solar Spectroscope Imager</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
           <t>['2002-004A', 'SMEX/RHESSI', 'Small Explorer/RHESSI', 'HESSI', 'Reuven Ramaty High Energy Solar Spectroscopic Imager']</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>Reuven Ramaty High Energy Solar Spectroscope Imager</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
+          <t>S-Cubed A</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
           <t>['Explorer 45', 'SSS-A']</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>S-Cubed A</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
+          <t>SAC-C Project</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
           <t>['Satélite de Aplicaciones Científicas-C', 'Scientific Application Satellite-C', 'Oersted-2', 'NSSDC ID: 2000-075B']</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>SAC-C Project</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>San Fernando Observatory</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>San Fernando Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>San Marco-DL</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>San Marco-DL</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>SDIC</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>SDIC</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Spherical Elementary Current Systems</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Spherical Elementary Current Systems</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Sodankylä Geophysical Observatory</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Sodankylä Geophysical Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Siple Experiment</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Siple Experiment</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>SME</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>SME</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Solar wind-Magnetosphere-Ionosphere Link Explorer (SMILE)</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Solar wind-Magnetosphere-Ionosphere Link Explorer (SMILE)</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Student Nitric Oxide Explorer</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Student Nitric Oxide Explorer</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>SOLIS</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>SOLIS</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
+          <t>Solar Radiation and Climate Experiment</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
           <t>['2003-004A', 'SOlar Radiation and Climate Experiment']</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Solar Radiation and Climate Experiment</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>LOFAR FR606 High Band Array</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>LOFAR FR606 High Band Array</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>LOFAR FR606 Low Band Array</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>LOFAR FR606 Low Band Array</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Nancay Decameter Array</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Nancay Decameter Array</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>NenuFAR</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>NenuFAR</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Nancay Radioheliograph</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Nancay Radioheliograph</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Nancay Radioheliograph</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Nancay Radioheliograph</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>ORFEES</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>ORFEES</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>ST5 Mission</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>ST5 Mission</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Solar-Terrestrial Relations Observatory</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Solar-Terrestrial Relations Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>STPSat-1</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>STPSat-1</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>SuperDARN</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>SuperDARN</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>SuperMAG</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>SuperMAG</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>TALO</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>TALO</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
+          <t>Time History of Events and Macroscale Interactions during Substorms</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
           <t>['MIDEX/THEMIS']</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>Time History of Events and Macroscale Interactions during Substorms</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
+          <t>Time History of Events and Macroscale Interactions during Substorms A</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
           <t>['Explorer 85', '2007-004A', 'MIDEX/THEMIS', 'THEMIS-P5', '30580']</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>Time History of Events and Macroscale Interactions during Substorms A</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
+          <t>Time History of Events and Macroscale Interactions during Substorms B</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
           <t>['Explorer 86', '2007-004B', 'MIDEX/THEMIS', 'THEMIS-P1', 'ARTEMIS-P1', '30581']</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Time History of Events and Macroscale Interactions during Substorms B</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
+          <t>Time History of Events and Macroscale Interactions during Substorms C</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
           <t>['Explorer 87', '2007-004C', 'MIDEX/THEMIS', 'THEMIS-P2', 'ARTEMIS-P2', '30582']</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>Time History of Events and Macroscale Interactions during Substorms C</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
+          <t>Time History of Events and Macroscale Interactions during Substorms D</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
           <t>['Explorer 88', '2007-004D', 'MIDEX/THEMIS', 'THEMIS-P3', '30797']</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>Time History of Events and Macroscale Interactions during Substorms D</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
+          <t>Time History of Events and Macroscale Interactions during Substorms E</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
           <t>['Explorer 89', '2007-004E', 'MIDEX/THEMIS', 'THEMIS-P4', '30798']</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>Time History of Events and Macroscale Interactions during Substorms E</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>THEMIS-Associated Ground Magnetometer Stations</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>THEMIS-Associated Ground Magnetometer Stations</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
+          <t>Canadian Magnetometer Array</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
           <t>['NASA THEMIS CANMAG Ground Stations']</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>Canadian Magnetometer Array</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>THULE</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>THULE</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
+          <t>Thermosphere-Ionosphere-Mesosphere Energetics and Dynamics</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
           <t>['2001-055B', 'Thermosphere Ionosphere Mesosphere Energetics and Dynamics']</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>Thermosphere-Ionosphere-Mesosphere Energetics and Dynamics</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>TIROSN</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>TIROSN</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Transition Region Explorer (TREx)</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Transition Region Explorer (TREx)</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Two Wide-angle Imaging Neutral Atom Spectrometers</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Two Wide-angle Imaging Neutral Atom Spectrometers</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>TWINS 1</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>TWINS 1</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>TWINS 2</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>TWINS 2</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Upper Atmosphere Research Satellite</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Upper Atmosphere Research Satellite</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>University of New Hampshire Observatory</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>University of New Hampshire Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
+          <t>Vega Mission</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
           <t>['Venera-Halley']</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr">
-        <is>
-          <t>Vega Mission</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Venus Express</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Venus Express</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Voyager 1 &amp; 2</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Voyager 1 &amp; 2</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Abinger Ground Observatory</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Abinger Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Abisko Ground Observatory</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Abisko Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Addis Ababa Ground Observatory</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Addis Ababa Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Agincourt Ground Observatory</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Agincourt Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Alert Ground Observatory</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Alert Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Alibag Ground Observatory</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Alibag Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Alice Springs Ground Observatory</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Alice Springs Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Alma Ata Ground Observatory</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Alma Ata Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Almeria Ground Observatory</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Almeria Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Amatsia Ground Observatory</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Amatsia Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Amberley Ground Observatory</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Amberley Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Anchorage Ground Observatory</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Anchorage Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Annamalainagar Ground Observatory</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Annamalainagar Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Antananarivo Ground Observatory</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Antananarivo Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Apia Ground Observatory</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Apia Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Arctowski Ground Observatory</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Arctowski Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Arkhangelsk Ground Observatory</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Arkhangelsk Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Arti Ground Observatory</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Arti Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Ascension Ground Observatory</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Ascension Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Aso Ground Observatory</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Aso Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Baguio Ground Observatory</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Baguio Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Baker Lake Ground Observatory</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Baker Lake Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Bangui Ground Observatory</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Bangui Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Bar Gyora Ground Observatory</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Bar Gyora Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Barrow Ground Observatory</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Barrow Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Bay St. Louis Ground Observatory</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Bay St. Louis Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Bear Island Ground Observatory</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Bear Island Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Beijing Ground Observatory</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Beijing Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Beijing Ming Tombs Ground Observatory</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Beijing Ming Tombs Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Beloit Ground Observatory</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Beloit Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Belsk Ground Observatory</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Belsk Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Bereznyaki Ground Observatory</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Bereznyaki Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Big Delta Ground Observatory</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Big Delta Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Borok Ground Observatory</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Borok Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Boulder Ground Observatory</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Boulder Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Brorfelde Ground Observatory</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Brorfelde Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Budkov Ground Observatory</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Budkov Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Burlington Ground Observatory</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Burlington Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Byrd Station Ground Observatory</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Byrd Station Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Cambridge Bay Ground Observatory</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Cambridge Bay Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Canberra Ground Observatory</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Canberra Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Cape Chelyuskin Ground Observatory</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Cape Chelyuskin Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Cape Town Ground Observatory</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Cape Town Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Cape Wellen Ground Observatory</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Cape Wellen Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Carrollton Ground Observatory</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Carrollton Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Casey Ground Observatory</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Casey Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Castellaccio Ground Observatory</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Castellaccio Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Chambon-la-Foret Ground Observatory</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Chambon-la-Foret Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Changchun Ground Observatory</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Changchun Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Characato Ground Observatory</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Characato Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Charcot Ground Observatory</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Charcot Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Charters Towers Ground Observatory</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Charters Towers Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Cheltenham Ground Observatory</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Cheltenham Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Chengdu Ground Observatory</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Chengdu Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Chichijima Ground Observatory</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Chichijima Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Coimbra Ground Observatory</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Coimbra Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>College Ground Observatory</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>College Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Dallas Ground Observatory</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Dallas Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Davao Ground Observatory</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Davao Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Davis Ground Observatory</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Davis Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>De Bilt Ground Observatory</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>De Bilt Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Del Rio Ground Observatory</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Del Rio Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Dixon Ground Observatory</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Dixon Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Dombas Ground Observatory</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Dombas Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Dourbes Ground Observatory</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Dourbes Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Dumont d'Urville Ground Observatory</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Dumont d'Urville Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Dusheti Ground Observatory</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Dusheti Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Easter Island Ground Observatory</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Easter Island Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Ebro Ground Observatory</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Ebro Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Eights Ground Observatory</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Eights Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Eilat Ground Observatory</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Eilat Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Esashi Ground Observatory</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Esashi Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Eskdalemuir Ground Observatory</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Eskdalemuir Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Etaiyapuram Ground Observatory</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Etaiyapuram Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Eyrewell Ground Observatory</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Eyrewell Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Fanning Ground Observatory</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Fanning Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Faraday Islands Ground Observatory</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Faraday Islands Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Fort Churchill Ground Observatory</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Fort Churchill Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Fredericksburg Ground Observatory</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Fredericksburg Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Freetown Ground Observatory</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Freetown Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Fresno Ground Observatory</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Fresno Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Fuquene Ground Observatory</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Fuquene Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Furstenfeldbruck Ground Observatory</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Furstenfeldbruck Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Glenlea Ground Observatory</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Glenlea Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Gnangara Ground Observatory</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Gnangara Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Godhavn Ground Observatory</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Godhavn Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Golmud Ground Observatory</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Golmud Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Gornotayezhnaya Ground Observatory</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Gornotayezhnaya Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Grahamstown Ground Observatory</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Grahamstown Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Great Whale River Ground Observatory</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Great Whale River Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Grocka Ground Observatory</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Grocka Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Guam Ground Observatory</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Guam Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Guangzhou Ground Observatory</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Guangzhou Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Guimar Ground Observatory</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Guimar Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Halley Bay Ground Observatory</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Halley Bay Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Hartebeesthoek Ground Observatory</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Hartebeesthoek Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Hartland Ground Observatory</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Hartland Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Hatizyo Ground Observatory</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Hatizyo Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Havana Ground Observatory</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Havana Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Heiss Island Ground Observatory</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Heiss Island Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Hel Ground Observatory</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Hel Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Helwan Ground Observatory</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Helwan Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Hermanus</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Hermanus</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Hollandia Ground Observatory</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Hollandia Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Honolulu</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Honolulu</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Hornsund Ground Observatory</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Hornsund Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Huancayo Ground Observatory</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Huancayo Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Hurbanovo Ground Observatory</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Hurbanovo Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Hyderabad Ground Observatory</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Hyderabad Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Ibadan Ground Observatory</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Ibadan Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Iqaluit Ground Observatory</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Iqaluit Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Istanbul Kandilli Ground Observatory</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Istanbul Kandilli Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Jaipur Ground Observatory</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Jaipur Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Jarvis Island Ground Observatory</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Jarvis Island Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Kakadu Ground Observatory</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Kakadu Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Kakioka</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Kakioka</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Kanoya Ground Observatory</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Kanoya Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Kanozan Ground Observatory</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Kanozan Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Karachi Ground Observatory</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Karachi Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Kashi Ground Observatory</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Kashi Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Kiev Ground Observatory</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Kiev Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Kiruna Ground Observatory</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Kiruna Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Kodaikanal Ground Observatory</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Kodaikanal Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Koror Ground Observatory</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Koror Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Kourou Ground Observatory</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Kourou Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Kr. Pakhra Ground Observatory</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Kr. Pakhra Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>La Quiaca Ground Observatory</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>La Quiaca Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Lanzhou Ground Observatory</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Lanzhou Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>L'Aquila Ground Observatory</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>L'Aquila Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Las Mesas Ground Observatory</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Las Mesas Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Leadville Ground Observatory</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Leadville Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Learmonth Ground Observatory</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Learmonth Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Leirvogur Ground Observatory</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Leirvogur Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Leningradskaya Ground Observatory</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Leningradskaya Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Lerwick Ground Observatory</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Lerwick Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Little America Ground Observatory</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Little America Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Livingston Island Ground Observatory</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Livingston Island Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Logrono Ground Observatory</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Logrono Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Loparskoe Ground Observatory</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Loparskoe Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Lovo Ground Observatory</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Lovo Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Luanda Capelo Ground Observatory</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Luanda Capelo Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Lunping Ground Observatory</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Lunping Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Lviv Ground Observatory</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Lviv Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Lwiro Ground Observatory</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Lwiro Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Macquarie Island Ground Observatory</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Macquarie Island Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Magadan Ground Observatory</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Magadan Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Manhay Ground Observatory</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Manhay Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Manzhouli Ground Observatory</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Manzhouli Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Maputo Ground Observatory</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Maputo Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Martin de Vivies Ground Observatory</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Martin de Vivies Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Mawson Ground Observatory</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Mawson Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>MBour Ground Observatory</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>MBour Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Meanook Ground Observatory</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Meanook Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Memambetsu Ground Observatory</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Memambetsu Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Midway Ground Observatory</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Midway Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Minck Ground Observatory</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Minck Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Mirny Ground Observatory</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Mirny Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Misallat Ground Observatory</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Misallat Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Mizusawa Ground Observatory</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Mizusawa Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Moca Ground Observatory</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Moca Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Molodezhnaya Ground Observatory</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Molodezhnaya Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Monte Capellino Ground Observatory</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Monte Capellino Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Mould Bay Ground Observatory</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Mould Bay Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Muntinlupa Ground Observatory</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Muntinlupa Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Murchison Bay Ground Observatory</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Murchison Bay Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Nagpur Ground Observatory</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Nagpur Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Nagycenk Ground Observatory</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Nagycenk Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Nairobi Ground Observatory</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Nairobi Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Nampula Ground Observatory</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Nampula Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Narsarsuaq Ground Observatory</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Narsarsuaq Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Neumayer Station Ground Observatory</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Neumayer Station Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Newport Ground Observatory</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Newport Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Niemegk Ground Observatory</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Niemegk Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Norway Station Ground Observatory</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Norway Station Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Novokazalinsk Ground Observatory</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Novokazalinsk Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Novolazarevskaya Ground Observatory</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Novolazarevskaya Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Novosibirsk, Klyuch Ground Observatory</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Novosibirsk, Klyuch Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Nurmijarvi Ground Observatory</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Nurmijarvi Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Oasis Ground Observatory</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Oasis Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Ottawa Ground Observatory</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Ottawa Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Pamatai Ground Observatory</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Pamatai Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Panagyurishte Ground Observatory</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Panagyurishte Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Paramaribo Ground Observatory</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Paramaribo Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Paratunka Ground Observatory</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Paratunka Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Patrony Ground Observatory</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Patrony Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Penteli Ground Observatory</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Penteli Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Phuthuy Ground Observatory</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Phuthuy Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Pilar Ground Observatory</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Pilar Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Pionerskaya Ground Observatory</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Pionerskaya Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Plateau Ground Observatory</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Plateau Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Podkamennaya Ground Observatory</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Podkamennaya Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Pondicherry Ground Observatory</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Pondicherry Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Port Alfred Ground Observatory</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Port Alfred Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Port aux Francais Ground Observatory</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Port aux Francais Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Port Moresby Ground Observatory</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Port Moresby Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Port Stanley Ground Observatory</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Port Stanley Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Poste de la Baleine Ground Observatory</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Poste de la Baleine Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Price Ground Observatory</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Price Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Pruhonice Ground Observatory</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Pruhonice Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Qianling Ground Observatory</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Qianling Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Qiongzhong Ground Observatory</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Qiongzhong Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Qsaybeh Ground Observatory</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Qsaybeh Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Quanzhou Ground Observatory</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Quanzhou Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Quetta Ground Observatory</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Quetta Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Resolute Ground Observatory</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Resolute Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Roburent Ground Observatory</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Roburent Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Roi Baudouin Ground Observatory</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Roi Baudouin Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Rude Skov Ground Observatory</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Rude Skov Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Sabhawala Ground Observatory</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Sabhawala Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Saint Johns Ground Observatory</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Saint Johns Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>San Fernando Ground Observatory</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>San Fernando Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>San Juan</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>San Juan</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>San Pablo-Toledo Ground Observatory</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>San Pablo-Toledo Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Sanae Ground Observatory</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Sanae Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Sao Miguel Ground Observatory</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Sao Miguel Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Sapa Ground Observatory</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Sapa Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Scott Base Ground Observatory</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Scott Base Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Shillong Ground Observatory</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Shillong Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Shumagin Ground Observatory</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Shumagin Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Silchar Ground Observatory</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Silchar Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Simosato Ground Observatory</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Simosato Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Sitka Ground Observatory</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Sitka Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Sodankyla Ground Observatory</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Sodankyla Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>South Georgia Ground Observatory</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>South Georgia Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>South Pole Ground Observatory</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>South Pole Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Stepanovka Ground Observatory</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Stepanovka Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Stonyhurst Ground Observatory</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Stonyhurst Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Sukkertoppen Ground Observatory</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Sukkertoppen Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Surlari Ground Observatory</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Surlari Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Swider Ground Observatory</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Swider Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Tahiti Ground Observatory</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Tahiti Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Talara Ground Observatory</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Talara Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Tamanrasset Ground Observatory</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Tamanrasset Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Tangerang Ground Observatory</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Tangerang Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Tatuoca Ground Observatory</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Tatuoca Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Tehran Ground Observatory</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Tehran Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Teoloyucan Ground Observatory</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Teoloyucan Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Thule Ground Observatory</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Thule Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Tihany Ground Observatory</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Tihany Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Tikhaya Bay Ground Observatory</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Tikhaya Bay Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Tirunelveli Ground Observatory</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Tirunelveli Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Tixie Bay Ground Observatory</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Tixie Bay Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Toledo Ground Observatory</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Toledo Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Tomsk Ground Observatory</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Tomsk Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Tondano Ground Observatory</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Tondano Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Tonghai Ground Observatory</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Tonghai Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Toolangi Ground Observatory</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Toolangi Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Trelew Ground Observatory</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Trelew Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Trivandrum Ground Observatory</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Trivandrum Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Tromso Ground Observatory</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Tromso Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Tsumeb Ground Observatory</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Tsumeb Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Tucson Ground Observatory</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Tucson Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Tuntungan Ground Observatory</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Tuntungan Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Ujjain Ground Observatory</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Ujjain Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Uppsala Ground Observatory</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Uppsala Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>V.Dubr. Ground Observatory</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>V.Dubr. Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Val Joyeux Ground Observatory</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Val Joyeux Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Valentia Ground Observatory</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Valentia Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Vannovskaya Ground Observatory</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Vannovskaya Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Vassouras Ground Observatory</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Vassouras Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Victoria Ground Observatory</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Victoria Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Vieques Ground Observatory</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Vieques Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Visakhapatnam Ground Observatory</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Visakhapatnam Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Vostok Ground Observatory</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Vostok Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Voyeykovo Ground Observatory</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Voyeykovo Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Watheroo Ground Observatory</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Watheroo Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Whiteshell Ground Observatory</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Whiteshell Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Wien Kobenzl Ground Observatory</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Wien Kobenzl Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Wilkes Ground Observatory</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Wilkes Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Wingst Ground Observatory</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Wingst Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Witteveen Ground Observatory</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Witteveen Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Wuhan Ground Observatory</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Wuhan Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Y. Basar Ground Observatory</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Y. Basar Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Yakutsk Ground Observatory</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Yakutsk Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Yazhno Sakhalinsk Ground Observatory</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Yazhno Sakhalinsk Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Yellowknife Ground Observatory</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Yellowknife Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Zaymishche Ground Observatory</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Zaymishche Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Zo-Se Ground Observatory</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Zo-Se Ground Observatory</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>WSO</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>WSO</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>YNAO</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>YNAO</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>['']</t>
+          <t>Zond 3</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Zond 3</t>
+          <t>['']</t>
         </is>
       </c>
     </row>
